--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4485CE-6E6C-4F10-A089-DCA0EFF300FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D6ECDE-1BE5-4308-8CE1-B86F06209956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D6ECDE-1BE5-4308-8CE1-B86F06209956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E51DBCE-4B4A-42C2-87CB-2096009187DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E51DBCE-4B4A-42C2-87CB-2096009187DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA599F2E-F220-467B-BF92-01E3AE742948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -49,6 +49,20 @@
     <author>Luiz Antunes</author>
   </authors>
   <commentList>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{94A30B7F-12F9-43F3-A32E-C175504BAE44}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t>LC - Diana - 24</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A9" authorId="0" shapeId="0" xr:uid="{F8956361-7AD5-407C-B4CE-99CFD7384890}">
       <text>
         <r>
@@ -2195,7 +2209,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2248,6 +2262,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="13">

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E0ABB6-CCD3-4F40-A802-9E5128DC2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453E6E3D-02E1-4474-9524-133F2FC0205F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -14845,7 +14845,7 @@
         <v>24</v>
       </c>
       <c r="F189" s="146" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>577</v>

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453E6E3D-02E1-4474-9524-133F2FC0205F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E0ABB6-CCD3-4F40-A802-9E5128DC2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -14845,7 +14845,7 @@
         <v>24</v>
       </c>
       <c r="F189" s="146" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>577</v>

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E0ABB6-CCD3-4F40-A802-9E5128DC2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35A627-5494-48E6-8BC3-D2A210EDC0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P4" s="61">
         <f>SUMIFS(L:L,B:B,"Livro",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>44617</v>
+        <v>44729</v>
       </c>
       <c r="Q4" s="62">
         <f>SUMIFS(L:L,B:B,"HQ",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="S4" s="62">
         <f>SUMIFS(L:L,K:K,"Físico",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>30493</v>
+        <v>30605</v>
       </c>
       <c r="T4" s="62">
         <f>SUMIFS(L:L,K:K,"Digital",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="U4" s="63">
         <f>SUM(P4:R4)</f>
-        <v>51093</v>
+        <v>51205</v>
       </c>
       <c r="V4" s="63">
         <f>COUNTIFS(C:C,"*(*",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W4" s="64">
         <f>SUM(W7:W22)/15</f>
-        <v>9.3211717443920445</v>
+        <v>9.3416283653966108</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -6032,15 +6032,22 @@
       <c r="H8" s="7">
         <v>46293</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="52"/>
+      <c r="I8" s="7">
+        <v>46296</v>
+      </c>
+      <c r="J8" s="52">
+        <f t="shared" ref="J8:J52" si="0">IF(I8="", "", I8 - H8 + 1)</f>
+        <v>4</v>
+      </c>
       <c r="K8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="3">
         <v>112</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3">
+        <v>4</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="38">
         <v>2012</v>
@@ -6107,7 +6114,7 @@
         <v>46291</v>
       </c>
       <c r="J9" s="52">
-        <f t="shared" ref="J9:J52" si="0">IF(I9="", "", I9 - H9 + 1)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="K9" s="7" t="s">
@@ -7139,7 +7146,7 @@
       </c>
       <c r="P22" s="57">
         <f>COUNTIFS(B:B,"Livro",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q22" s="40">
         <f>COUNTIFS(B:B,"HQ",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
@@ -7151,7 +7158,7 @@
       </c>
       <c r="S22" s="40">
         <f>COUNTIFS(K:K,"Físico",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" s="40">
         <f>COUNTIFS(K:K,"Digital",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
@@ -7159,15 +7166,15 @@
       </c>
       <c r="U22" s="40">
         <f>COUNTIFS(I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V22" s="40">
         <f>SUMIFS(L:L,I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>6087</v>
+        <v>6199</v>
       </c>
       <c r="W22" s="58">
         <f>V22/365</f>
-        <v>16.676712328767124</v>
+        <v>16.983561643835618</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
@@ -7330,7 +7337,7 @@
       </c>
       <c r="P25" s="61">
         <f t="shared" ref="P25:V25" si="1">SUM(P7:P22)</f>
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q25" s="62">
         <f t="shared" si="1"/>
@@ -7342,7 +7349,7 @@
       </c>
       <c r="S25" s="62">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T25" s="62">
         <f t="shared" si="1"/>
@@ -7350,15 +7357,15 @@
       </c>
       <c r="U25" s="62">
         <f t="shared" si="1"/>
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V25" s="63">
         <f t="shared" si="1"/>
-        <v>51093</v>
+        <v>51205</v>
       </c>
       <c r="W25" s="42">
         <f>SUM(U25)/16</f>
-        <v>11.5625</v>
+        <v>11.625</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -7640,7 +7647,7 @@
       </c>
       <c r="T30" s="110">
         <f>COUNTIF(M:M,4)</f>
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
@@ -8050,7 +8057,7 @@
       </c>
       <c r="P37" s="46">
         <f>SUMPRODUCT(--(MONTH(I2:I924)=10))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R37" s="110" t="s">
         <v>345</v>
@@ -8060,7 +8067,7 @@
       </c>
       <c r="T37" s="110">
         <f>SUM(T28:T36)</f>
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -8210,7 +8217,7 @@
       </c>
       <c r="P40" s="48">
         <f>SUM(P28:P39)</f>
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -14845,7 +14852,7 @@
         <v>24</v>
       </c>
       <c r="F189" s="146" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>577</v>
@@ -17862,7 +17869,7 @@
       </c>
       <c r="Y13" s="125">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="Z13" s="74"/>
     </row>
@@ -18108,7 +18115,7 @@
       </c>
       <c r="Y16" s="85">
         <f>AVERAGE(Y4:Y15)</f>
-        <v>0.96354166666666663</v>
+        <v>0.96875</v>
       </c>
       <c r="Z16" s="74"/>
     </row>
@@ -18207,7 +18214,7 @@
       </c>
       <c r="Y18" s="107">
         <f>SUM(D16,F16,H16,J16,L16,N16,P16,R16,T16,V16,D31,F31,H31,J31,L31,N31,P31)</f>
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z18" s="90"/>
     </row>
@@ -18859,7 +18866,7 @@
       </c>
       <c r="N28" s="79">
         <f>COUNTIFS('Livros Finalizados'!$I:$I,"&gt;=01/10/2026",'Livros Finalizados'!$I:$I,"&lt;=31/10/2026")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="80" t="s">
         <v>203</v>
@@ -19060,7 +19067,7 @@
       </c>
       <c r="N31" s="82">
         <f>SUM(N19:N30)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O31" s="83" t="s">
         <v>2</v>

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35A627-5494-48E6-8BC3-D2A210EDC0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E0ABB6-CCD3-4F40-A802-9E5128DC2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P4" s="61">
         <f>SUMIFS(L:L,B:B,"Livro",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>44729</v>
+        <v>44617</v>
       </c>
       <c r="Q4" s="62">
         <f>SUMIFS(L:L,B:B,"HQ",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="S4" s="62">
         <f>SUMIFS(L:L,K:K,"Físico",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>30605</v>
+        <v>30493</v>
       </c>
       <c r="T4" s="62">
         <f>SUMIFS(L:L,K:K,"Digital",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="U4" s="63">
         <f>SUM(P4:R4)</f>
-        <v>51205</v>
+        <v>51093</v>
       </c>
       <c r="V4" s="63">
         <f>COUNTIFS(C:C,"*(*",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W4" s="64">
         <f>SUM(W7:W22)/15</f>
-        <v>9.3416283653966108</v>
+        <v>9.3211717443920445</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -6032,22 +6032,15 @@
       <c r="H8" s="7">
         <v>46293</v>
       </c>
-      <c r="I8" s="7">
-        <v>46296</v>
-      </c>
-      <c r="J8" s="52">
-        <f t="shared" ref="J8:J52" si="0">IF(I8="", "", I8 - H8 + 1)</f>
-        <v>4</v>
-      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="3">
         <v>112</v>
       </c>
-      <c r="M8" s="3">
-        <v>4</v>
-      </c>
+      <c r="M8" s="3"/>
       <c r="N8" s="1"/>
       <c r="O8" s="38">
         <v>2012</v>
@@ -6114,7 +6107,7 @@
         <v>46291</v>
       </c>
       <c r="J9" s="52">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J9:J52" si="0">IF(I9="", "", I9 - H9 + 1)</f>
         <v>5</v>
       </c>
       <c r="K9" s="7" t="s">
@@ -7146,7 +7139,7 @@
       </c>
       <c r="P22" s="57">
         <f>COUNTIFS(B:B,"Livro",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q22" s="40">
         <f>COUNTIFS(B:B,"HQ",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
@@ -7158,7 +7151,7 @@
       </c>
       <c r="S22" s="40">
         <f>COUNTIFS(K:K,"Físico",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" s="40">
         <f>COUNTIFS(K:K,"Digital",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
@@ -7166,15 +7159,15 @@
       </c>
       <c r="U22" s="40">
         <f>COUNTIFS(I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V22" s="40">
         <f>SUMIFS(L:L,I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>6199</v>
+        <v>6087</v>
       </c>
       <c r="W22" s="58">
         <f>V22/365</f>
-        <v>16.983561643835618</v>
+        <v>16.676712328767124</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
@@ -7337,7 +7330,7 @@
       </c>
       <c r="P25" s="61">
         <f t="shared" ref="P25:V25" si="1">SUM(P7:P22)</f>
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q25" s="62">
         <f t="shared" si="1"/>
@@ -7349,7 +7342,7 @@
       </c>
       <c r="S25" s="62">
         <f t="shared" si="1"/>
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T25" s="62">
         <f t="shared" si="1"/>
@@ -7357,15 +7350,15 @@
       </c>
       <c r="U25" s="62">
         <f t="shared" si="1"/>
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="V25" s="63">
         <f t="shared" si="1"/>
-        <v>51205</v>
+        <v>51093</v>
       </c>
       <c r="W25" s="42">
         <f>SUM(U25)/16</f>
-        <v>11.625</v>
+        <v>11.5625</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -7647,7 +7640,7 @@
       </c>
       <c r="T30" s="110">
         <f>COUNTIF(M:M,4)</f>
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
@@ -8057,7 +8050,7 @@
       </c>
       <c r="P37" s="46">
         <f>SUMPRODUCT(--(MONTH(I2:I924)=10))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R37" s="110" t="s">
         <v>345</v>
@@ -8067,7 +8060,7 @@
       </c>
       <c r="T37" s="110">
         <f>SUM(T28:T36)</f>
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -8217,7 +8210,7 @@
       </c>
       <c r="P40" s="48">
         <f>SUM(P28:P39)</f>
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -14852,7 +14845,7 @@
         <v>24</v>
       </c>
       <c r="F189" s="146" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>577</v>
@@ -17869,7 +17862,7 @@
       </c>
       <c r="Y13" s="125">
         <f t="shared" si="0"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="Z13" s="74"/>
     </row>
@@ -18115,7 +18108,7 @@
       </c>
       <c r="Y16" s="85">
         <f>AVERAGE(Y4:Y15)</f>
-        <v>0.96875</v>
+        <v>0.96354166666666663</v>
       </c>
       <c r="Z16" s="74"/>
     </row>
@@ -18214,7 +18207,7 @@
       </c>
       <c r="Y18" s="107">
         <f>SUM(D16,F16,H16,J16,L16,N16,P16,R16,T16,V16,D31,F31,H31,J31,L31,N31,P31)</f>
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Z18" s="90"/>
     </row>
@@ -18866,7 +18859,7 @@
       </c>
       <c r="N28" s="79">
         <f>COUNTIFS('Livros Finalizados'!$I:$I,"&gt;=01/10/2026",'Livros Finalizados'!$I:$I,"&lt;=31/10/2026")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="80" t="s">
         <v>203</v>
@@ -19067,7 +19060,7 @@
       </c>
       <c r="N31" s="82">
         <f>SUM(N19:N30)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O31" s="83" t="s">
         <v>2</v>

--- a/livros/Lista de Livros Finalizados.xlsx
+++ b/livros/Lista de Livros Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E0ABB6-CCD3-4F40-A802-9E5128DC2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB390E4-B2EC-4EA0-8E8D-8FE216849298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="786" xr2:uid="{3784A4AE-152C-4AF4-93D4-216D06209999}"/>
   </bookViews>
@@ -49,6 +49,20 @@
     <author>Luiz Antunes</author>
   </authors>
   <commentList>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{A5A71927-712E-4C25-BB01-8884A09B3012}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t>LC - Diana - 25</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A10" authorId="0" shapeId="0" xr:uid="{94A30B7F-12F9-43F3-A32E-C175504BAE44}">
       <text>
         <r>
@@ -460,7 +474,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="632">
   <si>
     <t>Nº</t>
   </si>
@@ -5806,7 +5820,7 @@
       </c>
       <c r="P4" s="61">
         <f>SUMIFS(L:L,B:B,"Livro",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>44617</v>
+        <v>45109</v>
       </c>
       <c r="Q4" s="62">
         <f>SUMIFS(L:L,B:B,"HQ",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5818,15 +5832,15 @@
       </c>
       <c r="S4" s="62">
         <f>SUMIFS(L:L,K:K,"Físico",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>30493</v>
+        <v>30837</v>
       </c>
       <c r="T4" s="62">
         <f>SUMIFS(L:L,K:K,"Digital",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
-        <v>20600</v>
+        <v>20748</v>
       </c>
       <c r="U4" s="63">
         <f>SUM(P4:R4)</f>
-        <v>51093</v>
+        <v>51585</v>
       </c>
       <c r="V4" s="63">
         <f>COUNTIFS(C:C,"*(*",I:I,"&gt;=01/01/2000",I:I,"&lt;=31/12/2099")</f>
@@ -5834,7 +5848,7 @@
       </c>
       <c r="W4" s="64">
         <f>SUM(W7:W22)/15</f>
-        <v>9.3211717443920445</v>
+        <v>9.4110347580906737</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -5845,22 +5859,22 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="F5" s="146" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H5" s="7">
-        <v>46294</v>
+        <v>46304</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="52"/>
@@ -5868,7 +5882,7 @@
         <v>27</v>
       </c>
       <c r="L5" s="3">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="1"/>
@@ -5881,32 +5895,39 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="F6" s="146" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H6" s="7">
-        <v>46294</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="52"/>
+        <v>46299</v>
+      </c>
+      <c r="I6" s="7">
+        <v>46303</v>
+      </c>
+      <c r="J6" s="52">
+        <f t="shared" ref="J6:J52" si="0">IF(I6="", "", I6 - H6 + 1)</f>
+        <v>5</v>
+      </c>
       <c r="K6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L6" s="3">
-        <v>116</v>
-      </c>
-      <c r="M6" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="M6" s="3">
+        <v>4</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="34" t="s">
         <v>3</v>
@@ -5961,15 +5982,22 @@
       <c r="H7" s="7">
         <v>46295</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="52"/>
+      <c r="I7" s="7">
+        <v>46303</v>
+      </c>
+      <c r="J7" s="52">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="K7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L7" s="3">
         <v>232</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <v>4</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="38">
         <v>2011</v>
@@ -6032,15 +6060,22 @@
       <c r="H8" s="7">
         <v>46293</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="52"/>
+      <c r="I8" s="7">
+        <v>46296</v>
+      </c>
+      <c r="J8" s="52">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="K8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="3">
         <v>112</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3">
+        <v>4</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="38">
         <v>2012</v>
@@ -6107,7 +6142,7 @@
         <v>46291</v>
       </c>
       <c r="J9" s="52">
-        <f t="shared" ref="J9:J52" si="0">IF(I9="", "", I9 - H9 + 1)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="K9" s="7" t="s">
@@ -7139,7 +7174,7 @@
       </c>
       <c r="P22" s="57">
         <f>COUNTIFS(B:B,"Livro",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q22" s="40">
         <f>COUNTIFS(B:B,"HQ",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
@@ -7151,23 +7186,23 @@
       </c>
       <c r="S22" s="40">
         <f>COUNTIFS(K:K,"Físico",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T22" s="40">
         <f>COUNTIFS(K:K,"Digital",I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U22" s="40">
         <f>COUNTIFS(I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V22" s="40">
         <f>SUMIFS(L:L,I:I,"&gt;=01/01/2026",I:I,"&lt;=31/12/2026")</f>
-        <v>6087</v>
+        <v>6579</v>
       </c>
       <c r="W22" s="58">
         <f>V22/365</f>
-        <v>16.676712328767124</v>
+        <v>18.024657534246575</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
@@ -7330,7 +7365,7 @@
       </c>
       <c r="P25" s="61">
         <f t="shared" ref="P25:V25" si="1">SUM(P7:P22)</f>
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q25" s="62">
         <f t="shared" si="1"/>
@@ -7342,23 +7377,23 @@
       </c>
       <c r="S25" s="62">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="T25" s="62">
         <f t="shared" si="1"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U25" s="62">
         <f t="shared" si="1"/>
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="V25" s="63">
         <f t="shared" si="1"/>
-        <v>51093</v>
+        <v>51585</v>
       </c>
       <c r="W25" s="42">
         <f>SUM(U25)/16</f>
-        <v>11.5625</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -7640,7 +7675,7 @@
       </c>
       <c r="T30" s="110">
         <f>COUNTIF(M:M,4)</f>
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
@@ -8050,7 +8085,7 @@
       </c>
       <c r="P37" s="46">
         <f>SUMPRODUCT(--(MONTH(I2:I924)=10))</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R37" s="110" t="s">
         <v>345</v>
@@ -8060,7 +8095,7 @@
       </c>
       <c r="T37" s="110">
         <f>SUM(T28:T36)</f>
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -8210,7 +8245,7 @@
       </c>
       <c r="P40" s="48">
         <f>SUM(P28:P39)</f>
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -14845,7 +14880,7 @@
         <v>24</v>
       </c>
       <c r="F189" s="146" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>577</v>
@@ -15196,27 +15231,57 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
+      <c r="A4" s="9">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G4" s="7">
+        <v>46299</v>
+      </c>
+      <c r="H4" s="7">
+        <v>46303</v>
+      </c>
+      <c r="I4" s="52">
+        <f t="shared" ref="I4:I24" si="0">IF(H4="", "", H4 - G4 + 1)</f>
+        <v>5</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="10">
+        <v>148</v>
+      </c>
+      <c r="L4" s="112">
+        <v>4</v>
+      </c>
+      <c r="M4" s="112">
+        <v>4</v>
+      </c>
+      <c r="N4" s="112">
+        <f t="shared" ref="N4:N27" si="1">ROUND(AVERAGE(L4:M4)*2,0)/2</f>
+        <v>4</v>
+      </c>
       <c r="O4" s="1"/>
       <c r="P4" s="31" t="s">
         <v>2</v>
       </c>
       <c r="Q4" s="28">
         <f>SUMIFS(K:K,B:B,"Livro",H:H,"&gt;=01/01/2000",H:H,"&lt;=31/12/2099")</f>
-        <v>8370</v>
+        <v>8518</v>
       </c>
       <c r="R4" s="29">
         <f>SUMIFS(K:K,B:B,"HQ",H:H,"&gt;=01/01/2000",H:H,"&lt;=31/12/2099")</f>
@@ -15232,11 +15297,11 @@
       </c>
       <c r="U4" s="29">
         <f>SUMIFS(K:K,J:J,"Digital",H:H,"&gt;=01/01/2000",H:H,"&lt;=31/12/2099")</f>
-        <v>1241</v>
+        <v>1389</v>
       </c>
       <c r="V4" s="30">
         <f>SUM(Q4:S4)</f>
-        <v>8370</v>
+        <v>8518</v>
       </c>
       <c r="W4" s="23">
         <f>COUNTIFS(C:C,"*(*",H:H,"&gt;=01/01/2000",H:H,"&lt;=31/12/2099")</f>
@@ -15244,7 +15309,7 @@
       </c>
       <c r="X4" s="42">
         <f>SUM(X7:X9)/2</f>
-        <v>11.459495471217906</v>
+        <v>11.662235197245304</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -15273,7 +15338,7 @@
         <v>46284</v>
       </c>
       <c r="I5" s="52">
-        <f t="shared" ref="I5:I24" si="0">IF(H5="", "", H5 - G5 + 1)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="J5" s="7" t="s">
@@ -15289,7 +15354,7 @@
         <v>4</v>
       </c>
       <c r="N5" s="112">
-        <f t="shared" ref="N5:N27" si="1">ROUND(AVERAGE(L5:M5)*2,0)/2</f>
+        <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
       <c r="O5" s="1"/>
@@ -15583,7 +15648,7 @@
       </c>
       <c r="Q9" s="57">
         <f>COUNTIFS(B:B,"Livro",H:H,"&gt;=01/01/2026",H:H,"&lt;=31/12/2026")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R9" s="40">
         <f>COUNTIFS(B:B,"HQ",H:H,"&gt;=01/01/2026",H:H,"&lt;=31/12/2026")</f>
@@ -15599,19 +15664,19 @@
       </c>
       <c r="U9" s="40">
         <f>COUNTIFS(J:J,"Digital",H:H,"&gt;=01/01/2026",H:H,"&lt;=31/12/2026")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V9" s="40">
         <f>COUNTIFS(H:H,"&gt;=01/01/2026",H:H,"&lt;=31/12/2026")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W9" s="40">
         <f>SUMIFS(K:K,H:H,"&gt;=01/01/2026",H:H,"&lt;=31/12/2026")</f>
-        <v>2510</v>
+        <v>2658</v>
       </c>
       <c r="X9" s="58">
         <f>W9/365</f>
-        <v>6.8767123287671232</v>
+        <v>7.2821917808219174</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -15786,7 +15851,7 @@
       </c>
       <c r="Q12" s="20">
         <f t="shared" ref="Q12:W12" si="2">SUM(Q7:Q9)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="2"/>
@@ -15802,19 +15867,19 @@
       </c>
       <c r="U12" s="24">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12" s="24">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W12" s="23">
         <f t="shared" si="2"/>
-        <v>8370</v>
+        <v>8518</v>
       </c>
       <c r="X12" s="42">
         <f>SUM(V12)/3</f>
-        <v>8</v>
+        <v>8.3333333333333339</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -16001,7 +16066,7 @@
       </c>
       <c r="X15" s="109">
         <f>COUNTIF(F:F,"Diana")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -16136,7 +16201,7 @@
       </c>
       <c r="U17" s="110">
         <f>COUNTIF(N:N,4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17" s="110" t="s">
         <v>335</v>
@@ -16214,7 +16279,7 @@
       </c>
       <c r="X18" s="109">
         <f>SUM(X15:X17)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -16588,7 +16653,7 @@
       </c>
       <c r="Q24" s="46">
         <f>SUMPRODUCT(--(MONTH(H2:H745)=10))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" s="110" t="s">
         <v>345</v>
@@ -16598,7 +16663,7 @@
       </c>
       <c r="U24" s="110">
         <f>SUM(U15:U23)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -16760,7 +16825,7 @@
       </c>
       <c r="Q27" s="48">
         <f>SUM(Q15:Q26)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -16908,7 +16973,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="X7" formula="1"/>
-    <ignoredError sqref="N5:N28" formulaRange="1"/>
+    <ignoredError sqref="N4:N28" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17862,7 +17927,7 @@
       </c>
       <c r="Y13" s="125">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="Z13" s="74"/>
     </row>
@@ -18108,7 +18173,7 @@
       </c>
       <c r="Y16" s="85">
         <f>AVERAGE(Y4:Y15)</f>
-        <v>0.96354166666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="Z16" s="74"/>
     </row>
@@ -18207,7 +18272,7 @@
       </c>
       <c r="Y18" s="107">
         <f>SUM(D16,F16,H16,J16,L16,N16,P16,R16,T16,V16,D31,F31,H31,J31,L31,N31,P31)</f>
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Z18" s="90"/>
     </row>
@@ -18859,7 +18924,7 @@
       </c>
       <c r="N28" s="79">
         <f>COUNTIFS('Livros Finalizados'!$I:$I,"&gt;=01/10/2026",'Livros Finalizados'!$I:$I,"&lt;=31/10/2026")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" s="80" t="s">
         <v>203</v>
@@ -19060,7 +19125,7 @@
       </c>
       <c r="N31" s="82">
         <f>SUM(N19:N30)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O31" s="83" t="s">
         <v>2</v>
